--- a/data/trans_orig/IP24_R_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15911</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9324</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24695</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12384</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8487</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18145</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>109577</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100793</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>104517</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98756</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>108414</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>124077</t>
+          <t>107877</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115539</t>
+          <t>102437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130477</t>
+          <t>112199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>228592</t>
+          <t>217453</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218905</t>
+          <t>207415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236996</t>
+          <t>226043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139883</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19061</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12785</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27975</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14345</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8991</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21245</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>25275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43895</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>216860</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>207946</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>223136</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>176167</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>169267</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181521</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>234470</t>
+          <t>169566</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226483</t>
+          <t>163043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>241141</t>
+          <t>174683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>410638</t>
+          <t>386426</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>400325</t>
+          <t>375907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>418917</t>
+          <t>395059</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253707</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22806</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14836</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33480</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11193</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5622</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23962</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48725</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>143637</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132963</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151607</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>178392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>165623</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>183963</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159803</t>
+          <t>147190</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149222</t>
+          <t>141332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168050</t>
+          <t>151467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>338195</t>
+          <t>290827</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>323728</t>
+          <t>279480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>349255</t>
+          <t>299684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182868</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36541</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27265</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45845</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17924</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12262</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25898</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45365</t>
+          <t>44910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69146</t>
+          <t>67717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132835</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>123531</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>142111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>148907</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140933</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>154569</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,26%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>142557</t>
+          <t>147881</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130833</t>
+          <t>139745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151376</t>
+          <t>153730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>291464</t>
+          <t>280716</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278923</t>
+          <t>267819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>302704</t>
+          <t>290626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44882</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72726</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>129735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>602909</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>584041</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>617938</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>850</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>607982</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>591103</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>618947</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>660908</t>
+          <t>572514</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>642924</t>
+          <t>560397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676576</t>
+          <t>582782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1268890</t>
+          <t>1175422</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1247144</t>
+          <t>1154058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1289764</t>
+          <t>1195015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
